--- a/data/trans_orig/IP07A03-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07A03-Estudios-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de haber estado contento/a con su forma de ser, percibida por el adulto en 2007 (tasa de respuesta: 99,3%)</t>
+          <t>Menores según la frecuencia de haber estado contento/a con su forma de ser, percibida por el/la adulto/a [KIDSCREEN 20] en 2007 (tasa de respuesta: 99,3%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>25634</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>19940</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>30821</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>55,06%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>42,83%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>66,2%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>25695</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>20114</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>31219</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>20182</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>31954</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>50,71%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>39,69%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>61,61%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>25634</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>20217</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>30932</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>55,06%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43309</t>
+          <t>44180</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59232</t>
+          <t>59220</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>60,91%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>17609</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12990</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>23019</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>37,82%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>27,9%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>49,44%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>19629</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>14194</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>25297</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>13984</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>25205</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>38,74%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>28,01%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>49,92%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>17609</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>12802</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>23291</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>37,82%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29760</t>
+          <t>30455</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45320</t>
+          <t>44305</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>45,57%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1968</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5315</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>4,23%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>11,42%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>5351</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2568</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>9505</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2621</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>10,56%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,07%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>18,76%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1968</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>5343</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>4,23%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3987</t>
+          <t>3917</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12135</t>
+          <t>11972</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,31%</t>
         </is>
       </c>
     </row>
@@ -1061,107 +1061,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3624</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,78%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>680</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4359</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3397</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>9,36%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3417</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -1174,107 +1174,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3404</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>7,31%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>667</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3785</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>3385</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>8,13%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>2996</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>46558</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>46558</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>46558</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>50674</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>50674</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>50674</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>46558</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>46558</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>46558</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>131157</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>118377</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>143900</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>55,59%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>50,17%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>60,99%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>112682</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>100596</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>124289</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>100258</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>123674</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>55,2%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>49,28%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>60,89%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>131157</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>119550</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>143773</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>55,59%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>225481</t>
+          <t>227994</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>259684</t>
+          <t>260368</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>59,17%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>88987</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>77316</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>101048</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>37,72%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>32,77%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>42,83%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>77664</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>66153</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>89247</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>66733</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>88952</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>38,05%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>32,41%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>43,72%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>88987</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>76515</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>100812</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>37,72%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>150809</t>
+          <t>150776</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>184225</t>
+          <t>182559</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>41,49%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>14758</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9266</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>21751</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>6,26%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3,93%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>9,22%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>13129</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>8396</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>19554</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>8289</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>19479</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>6,43%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4,11%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>9,58%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>14758</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>9564</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>21284</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>6,26%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19928</t>
+          <t>21037</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>37088</t>
+          <t>37596</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -1743,72 +1743,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1036</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3190</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>642</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3502</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4439</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,31%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1036</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3435</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>482</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4792</t>
+          <t>4797</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>235938</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>235938</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>235938</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>305</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>204117</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>204117</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>204117</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>356</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>235938</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>235938</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>235938</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>31184</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>25341</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>37465</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>51,63%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>41,96%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>62,03%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>35147</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>28543</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>42213</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>28595</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>41093</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>52,57%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>42,69%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>63,14%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>31184</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>25092</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>37563</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>51,63%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>56953</t>
+          <t>57196</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>75371</t>
+          <t>75332</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>59,2%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>27198</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>21039</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>33595</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>45,03%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>34,84%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>55,63%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>25735</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>19512</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>32520</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>19551</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>32848</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>38,49%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>29,19%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>48,64%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>27198</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>20467</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>32795</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>45,03%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>43844</t>
+          <t>43407</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>62066</t>
+          <t>62172</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>48,86%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>5380</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3,33%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>8,91%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>5240</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>2278</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>10294</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>2291</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>9251</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>7,84%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>3,41%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>15,4%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>5898</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>3,33%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3488</t>
+          <t>3647</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12742</t>
+          <t>12840</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -2425,107 +2425,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>732</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3629</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4399</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,09%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>5,43%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>6,58%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>732</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>3670</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>732</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>3677</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>60394</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>60394</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>60394</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>66854</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>66854</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>66854</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>60394</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>60394</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>60394</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2768,72 +2768,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>187975</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>172822</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>202861</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>54,82%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>50,4%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>59,16%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>256</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>173524</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>158335</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>187878</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>161278</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>187795</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>53,95%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>49,23%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>58,41%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>187975</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>173317</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>203284</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>54,82%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>340408</t>
+          <t>340233</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>383221</t>
+          <t>382195</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,51%</t>
         </is>
       </c>
     </row>
@@ -2881,72 +2881,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>133794</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>117965</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>148718</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>39,02%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>34,4%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>43,37%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>123027</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>109105</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>137413</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>109082</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>136190</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>38,25%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>33,92%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>42,72%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>133794</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>118573</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>148254</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>39,02%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>236714</t>
+          <t>237426</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>278026</t>
+          <t>276403</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>41,59%</t>
         </is>
       </c>
     </row>
@@ -2994,72 +2994,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>18739</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>13055</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>26532</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>5,46%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>3,81%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>7,74%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>23720</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>17318</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>32985</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>17117</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>31925</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>7,37%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>5,38%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>10,26%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>18739</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>12865</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>26881</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>5,46%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>33481</t>
+          <t>33490</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>54172</t>
+          <t>53663</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -3107,72 +3107,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1715</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>4777</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>1374</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>4949</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>4730</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,43%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>1715</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>5203</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6908</t>
+          <t>6804</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -3220,92 +3220,92 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>2689</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="R26" s="2" t="inlineStr">
         <is>
           <t>667</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="S26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>2691</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3349</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3333,57 +3333,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>342890</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>342890</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>342890</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>477</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>321645</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>321645</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>321645</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>515</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>342890</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>342890</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>342890</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3496,13 +3496,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de haber estado contento/a con su forma de ser, percibida por el adulto en 2012 (tasa de respuesta: 98,02%)</t>
+          <t>Menores según la frecuencia de haber estado contento/a con su forma de ser, percibida por el/la adulto/a [KIDSCREEN 20] en 2012 (tasa de respuesta: 98,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3513,7 +3513,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3681,72 +3681,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>23452</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>17652</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>29035</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>51,15%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>38,5%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>63,32%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>30777</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>24780</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>36268</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>24937</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>36493</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>57,98%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>46,68%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>68,32%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>23452</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>17939</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>29109</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>51,15%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45747</t>
+          <t>45678</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62006</t>
+          <t>62459</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>63,13%</t>
         </is>
       </c>
     </row>
@@ -3794,72 +3794,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16837</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11775</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22139</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>36,72%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>25,68%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>48,28%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>19023</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>13586</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>24765</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>13300</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>25014</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>35,84%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>25,59%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>46,65%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>16837</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>11573</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>22558</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>36,72%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28152</t>
+          <t>27931</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44474</t>
+          <t>43586</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>44,06%</t>
         </is>
       </c>
     </row>
@@ -3907,72 +3907,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4940</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2409</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9491</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>10,77%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>5,25%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>20,7%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>747</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4669</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4652</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>1,41%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>8,8%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>4940</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>10,77%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>4,58%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2522</t>
+          <t>2516</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10927</t>
+          <t>10802</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -4025,102 +4025,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3906</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,52%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>1058</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4216</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5221</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,99%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,94%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>624</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>9,84%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1681</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3721</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>5846</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>8,12%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1681</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>5886</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -4133,107 +4133,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>1478</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5144</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5226</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>2,78%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,69%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>9,85%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1478</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>4966</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1478</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4426</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -4246,57 +4246,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>45853</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>45853</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>45853</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>53083</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>53083</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>53083</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>45853</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>45853</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>45853</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4363,72 +4363,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>124211</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>111774</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>136963</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>54,31%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>48,87%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>59,88%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>143</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>101063</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>88781</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>112634</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>88294</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>112405</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>49,33%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>43,33%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>54,98%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>124211</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>112768</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>137442</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>54,31%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>207446</t>
+          <t>207380</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>242084</t>
+          <t>242403</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>55,91%</t>
         </is>
       </c>
     </row>
@@ -4476,72 +4476,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>87707</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>76145</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>101069</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>38,35%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>33,29%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>44,19%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>83336</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>72176</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>94653</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>71668</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>96490</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>40,68%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>35,23%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>46,2%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>87707</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>75921</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>100066</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>38,35%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>155154</t>
+          <t>154602</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>188984</t>
+          <t>187442</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,23%</t>
         </is>
       </c>
     </row>
@@ -4589,72 +4589,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>12136</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7568</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>18019</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>5,31%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>7,88%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>19560</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>13419</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>26900</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>13018</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>27091</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>9,55%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,55%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>13,13%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>12136</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>7704</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>18212</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>5,31%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>24025</t>
+          <t>23067</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>41420</t>
+          <t>40042</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -4702,72 +4702,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3362</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1193</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7407</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,24%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>916</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4624</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4053</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,45%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3362</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1215</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7700</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1581</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8789</t>
+          <t>9073</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -4815,107 +4815,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1307</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4690</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>1307</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4044</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>4459</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1307</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>3983</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -4928,57 +4928,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>228723</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>228723</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>228723</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>293</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>204874</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>204874</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>204874</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>334</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>228723</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>228723</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>228723</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5045,72 +5045,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>29021</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>23300</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>35821</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>50,09%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>40,22%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>61,83%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>36768</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>29677</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>42549</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>30348</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>43035</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>57,98%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>46,8%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>67,09%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>29021</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>22053</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>35171</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>50,09%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>56480</t>
+          <t>56519</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74898</t>
+          <t>74003</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>60,98%</t>
         </is>
       </c>
     </row>
@@ -5158,72 +5158,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>26286</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>19669</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>32114</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>45,37%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>33,95%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>55,43%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>22534</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>16804</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>29609</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>16827</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>29738</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>35,53%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>26,5%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>46,69%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>26286</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>20691</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>33055</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>45,37%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40050</t>
+          <t>39936</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>58716</t>
+          <t>57632</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>47,49%</t>
         </is>
       </c>
     </row>
@@ -5271,72 +5271,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2625</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>730</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>6433</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>4,53%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>4116</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1530</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>8205</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1556</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>8781</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>6,49%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>12,94%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>2625</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>5980</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>4,53%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3384</t>
+          <t>3344</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11901</t>
+          <t>12570</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -5610,57 +5610,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>57933</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>57933</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>57933</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>63418</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>63418</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>63418</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>57933</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>57933</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>57933</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5727,72 +5727,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>176684</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>160931</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>190905</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>53,14%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>48,4%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>57,41%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>237</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>168607</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>152848</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>182134</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>153999</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>183038</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>52,46%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>47,56%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>56,67%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>176684</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>162372</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>191380</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>53,14%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>325855</t>
+          <t>324841</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>366879</t>
+          <t>365530</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>55,9%</t>
         </is>
       </c>
     </row>
@@ -5840,72 +5840,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>130830</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>117109</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>144742</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>39,35%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>35,22%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>43,53%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>179</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>124893</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>111662</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>140446</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>109965</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>139273</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>38,86%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>34,75%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>43,7%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>130830</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>116034</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>144522</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>39,35%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>235986</t>
+          <t>236071</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>276470</t>
+          <t>275556</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,14%</t>
         </is>
       </c>
     </row>
@@ -5953,72 +5953,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>19702</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>13439</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>27955</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>5,93%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>4,04%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>8,41%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>24422</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>17827</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>32521</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>16882</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>32118</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>7,6%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>5,55%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>10,12%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>19702</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>13530</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>27918</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>5,93%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>34890</t>
+          <t>35320</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>54790</t>
+          <t>56030</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -6066,72 +6066,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>3986</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1486</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>8221</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,47%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>1974</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>6159</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>7029</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,61%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>3986</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>1506</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>8531</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2548</t>
+          <t>2866</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11455</t>
+          <t>11646</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -6184,67 +6184,67 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>1307</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>4858</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
           <t>1478</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>5334</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5482</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,46%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>1307</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>4629</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>687</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6961</t>
+          <t>6956</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,7 +6274,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6292,57 +6292,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>332508</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>332508</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>332508</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>456</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>321375</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>321375</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>321375</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>332508</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>332508</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>332508</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6455,13 +6455,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de haber estado contento/a con su forma de ser, percibida por el adulto en 2016 (tasa de respuesta: 98,92%)</t>
+          <t>Menores según la frecuencia de haber estado contento/a con su forma de ser, percibida por el/la adulto/a [KIDSCREEN 20] en 2016 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6472,7 +6472,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6640,72 +6640,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>23466</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>18728</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>28392</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>65,24%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>52,07%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>78,94%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>15598</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>10629</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>20560</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>11367</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>20509</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>49,03%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>33,41%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>64,63%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>23466</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>18712</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>27793</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>65,24%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31945</t>
+          <t>32381</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45627</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>67,57%</t>
         </is>
       </c>
     </row>
@@ -6753,72 +6753,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9337</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5259</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>14277</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>25,96%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>14,62%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>39,7%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>12473</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>8032</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>17271</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>7932</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>17184</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>39,21%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>25,25%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>54,29%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>9337</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>5317</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>13992</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>25,96%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15904</t>
+          <t>16250</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28490</t>
+          <t>28509</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>42,06%</t>
         </is>
       </c>
     </row>
@@ -6866,72 +6866,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2272</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>660</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5566</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>6,32%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>15,47%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>3743</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1386</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7411</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1518</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>7494</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>11,76%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>23,3%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2272</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>668</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>5486</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>6,32%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2960</t>
+          <t>3126</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10292</t>
+          <t>10805</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,94%</t>
         </is>
       </c>
     </row>
@@ -6979,107 +6979,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4383</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,48%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>12,19%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>891</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4455</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>6578</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>12,39%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>891</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4656</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -7205,57 +7205,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>35967</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>35967</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>35967</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>31814</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>31814</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>31814</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>35967</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>35967</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>35967</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7322,72 +7322,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>153032</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>139792</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>166313</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>62,04%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>56,67%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>67,43%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>143270</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>129251</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>156343</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>129646</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>155589</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>57,18%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>51,58%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>62,4%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>153032</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>140405</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>164887</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>62,04%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>278681</t>
+          <t>276555</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>314207</t>
+          <t>314036</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>63,16%</t>
         </is>
       </c>
     </row>
@@ -7435,72 +7435,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>80983</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>67540</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>93788</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>32,83%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>27,38%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>38,02%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>130</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>90196</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>77031</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>104252</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>77719</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>102691</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>36,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>30,74%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>41,61%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>80983</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>69296</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>93485</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>32,83%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>153918</t>
+          <t>153434</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>188423</t>
+          <t>189122</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>38,04%</t>
         </is>
       </c>
     </row>
@@ -7548,72 +7548,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>11887</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7414</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>18916</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>4,82%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>7,67%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>11540</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6406</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>18506</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>6762</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>18197</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>4,61%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>7,39%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>11887</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>6916</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>17749</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>4,82%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16681</t>
+          <t>16754</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>32971</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -7661,72 +7661,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3796</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>5029</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2194</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>9629</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2148</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>9818</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,01%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,84%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>759</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4571</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2649</t>
+          <t>2684</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10941</t>
+          <t>11289</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -7774,92 +7774,92 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>524</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2902</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2448</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,21%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2647</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7887,57 +7887,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>246662</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>246662</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>246662</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>360</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>250559</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>250559</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>250559</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>337</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>246662</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>246662</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>246662</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8004,72 +8004,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>51672</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>43157</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>58092</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>66,19%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>55,29%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>74,42%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>49423</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>42443</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>55584</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>43065</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>56606</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>66,43%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>57,05%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>74,71%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>51672</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>44307</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>58370</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>66,19%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>90373</t>
+          <t>90790</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>110106</t>
+          <t>110152</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>72,25%</t>
         </is>
       </c>
     </row>
@@ -8117,72 +8117,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>24569</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>18103</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>32870</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>31,47%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>23,19%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>42,11%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>23524</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>17388</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>30676</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>16176</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>29826</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>31,62%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>23,37%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>41,23%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>24569</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>17698</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>31534</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>31,47%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38986</t>
+          <t>39090</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>58033</t>
+          <t>58407</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>38,31%</t>
         </is>
       </c>
     </row>
@@ -8230,72 +8230,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1820</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>4941</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>6,33%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>1451</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>4669</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5121</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>1,95%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>6,28%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>1820</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>549</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>5273</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1193</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7313</t>
+          <t>7547</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -8569,57 +8569,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>78061</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>78061</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>78061</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>74398</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>74398</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>74398</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>78061</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>78061</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>78061</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8686,72 +8686,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>228170</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>212505</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>242754</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>63,26%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>58,92%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>67,3%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>298</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>208291</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>192215</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>223049</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>193306</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>224777</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>58,38%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>53,88%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>62,52%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>309</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>228170</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>212706</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>243769</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>63,26%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>410405</t>
+          <t>412950</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>456424</t>
+          <t>456906</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>63,68%</t>
         </is>
       </c>
     </row>
@@ -8799,72 +8799,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>114890</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>100275</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>130886</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>31,85%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>27,8%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>36,29%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>126194</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>110795</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>140169</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>112068</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>140724</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>35,37%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>31,05%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>39,29%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>114890</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>99998</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>130097</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>31,85%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>220882</t>
+          <t>221615</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>266351</t>
+          <t>263587</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>36,74%</t>
         </is>
       </c>
     </row>
@@ -8917,67 +8917,67 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>15979</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>10154</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>23041</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>6,39%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
           <t>16734</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>11039</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>24910</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>10759</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>24571</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>4,69%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>6,98%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>15979</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>10670</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>22850</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>4,43%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>24410</t>
+          <t>24312</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>43942</t>
+          <t>42307</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -9025,72 +9025,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1650</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>5739</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>5029</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>2228</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>10489</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>2294</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>10638</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>1,41%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,94%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>1650</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>6714</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3467</t>
+          <t>3379</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12186</t>
+          <t>12031</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -9138,107 +9138,107 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>524</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>2468</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>2662</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,15%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>3119</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>2633</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -9251,57 +9251,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>360690</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>360690</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>360690</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>510</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>356772</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>356772</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>356772</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>495</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>360690</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>360690</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>360690</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
